--- a/workbooks/scenarios/ApplianceScenarios.xlsx
+++ b/workbooks/scenarios/ApplianceScenarios.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Appliance Age/Type</t>
+          <t>Appliance Age</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">

--- a/workbooks/scenarios/ApplianceScenarios.xlsx
+++ b/workbooks/scenarios/ApplianceScenarios.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L99"/>
+  <dimension ref="A1:L101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5770,6 +5770,114 @@
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Laundry finished around 6 PM in Harrisburg. When should I run the dryer?</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>260</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Dryer</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Rowhouse</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>4</v>
+      </c>
+      <c r="G100" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H100" t="n">
+        <v>9</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>6pm</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>6pm</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>10pm</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>6am</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>It's around 8 in the morning and I need to run the dishwasher in Doylestown. When should I start it?</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Doylestown, PA</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>210</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Dishwasher</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Townhouse</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>3</v>
+      </c>
+      <c r="G101" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="H101" t="n">
+        <v>6</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>8am</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>8am</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>2pm</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>11pm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/workbooks/scenarios/ApplianceScenarios.xlsx
+++ b/workbooks/scenarios/ApplianceScenarios.xlsx
@@ -696,7 +696,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>It's just past 5 PM — when should I run the dryer?</t>
+          <t>It's just past 5 PM, when should I run the dryer?</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -966,7 +966,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>It's around 7 in the evening — when should I run the dishwasher?</t>
+          <t>It's around 7 in the evening, when should I run the dishwasher?</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1290,7 +1290,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>It's getting close to midnight — when should I run the washing machine?</t>
+          <t>It's getting close to midnight, when should I run the washing machine?</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1344,7 +1344,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>It's just past 5 PM — when should I run the washer?</t>
+          <t>It's just past 5 PM, when should I run the washer?</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1776,7 +1776,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>It's past 1 in the morning — when should I run the dryer?</t>
+          <t>It's past 1 in the morning, when should I run the dryer?</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1992,7 +1992,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>It's just past midnight — when should I run the dishwasher?</t>
+          <t>It's just past midnight, when should I run the dishwasher?</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2262,7 +2262,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>It's around 8 at night — when should I run the dishwasher?</t>
+          <t>It's around 8 at night, when should I run the dishwasher?</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2640,7 +2640,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>It's just past 9 AM — when should I run the dryer?</t>
+          <t>It's just past 9 AM, when should I run the dryer?</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3126,7 +3126,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>It's just past 9 AM — when should I run the dryer?</t>
+          <t>It's just past 9 AM, when should I run the dryer?</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3342,7 +3342,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>It's around 5 in the evening — when should I run the washing machine?</t>
+          <t>It's around 5 in the evening, when should I run the washing machine?</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3450,7 +3450,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>It's just past 7 PM — when should I run the dryer?</t>
+          <t>It's just past 7 PM, when should I run the dryer?</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3612,7 +3612,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>It's late — just past 10 PM and I need to run the dryer. When should I start it?</t>
+          <t>It's late, just past 10 PM and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3774,7 +3774,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>It's getting close to midnight — when should I run the washing machine?</t>
+          <t>It's getting close to midnight, when should I run the washing machine?</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3936,7 +3936,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>It's just after 8 AM — when should I run the dishwasher?</t>
+          <t>It's just after 8 AM, when should I run the dishwasher?</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4368,7 +4368,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>It's nearly 11 at night — when should I run the washing machine?</t>
+          <t>It's nearly 11 at night, when should I run the washing machine?</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4530,7 +4530,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>It's late afternoon, just past 3 — when should I run the dishwasher?</t>
+          <t>It's late afternoon, just past 3, when should I run the dishwasher?</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5664,7 +5664,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>It's around 2 in the afternoon — when should I run the dryer?</t>
+          <t>It's around 2 in the afternoon, when should I run the dryer?</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -5718,7 +5718,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>I've just got home — it's around 6 PM — and I need to run the dishwasher. When should I start it?</t>
+          <t>I've just got home, it's around 6 PM, and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">

--- a/workbooks/scenarios/ApplianceScenarios.xlsx
+++ b/workbooks/scenarios/ApplianceScenarios.xlsx
@@ -696,7 +696,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>It's just past 5 PM, when should I run the dryer?</t>
+          <t>It's just past 5 PM. When should I run the dryer?</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -858,7 +858,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>It's mid-afternoon, about 2 and I'm trying to figure out when to start the dishwasher. When should I run it?</t>
+          <t>It's mid-afternoon, about 2, and I'm trying to figure out when to start the dishwasher. When should I run it?</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>It's mid-afternoon, about 2 and I need to run the dryer. When should I start it?</t>
+          <t>It's mid-afternoon, about 2, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -966,7 +966,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>It's around 7 in the evening, when should I run the dishwasher?</t>
+          <t>It's around 7 in the evening. When should I run the dishwasher?</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1074,7 +1074,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>It's mid-afternoon, about 2 and I'm trying to figure out when to start the washing machine. When should I run it?</t>
+          <t>It's mid-afternoon, about 2, and I'm trying to figure out when to start the washing machine. When should I run it?</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1290,7 +1290,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>It's getting close to midnight, when should I run the washing machine?</t>
+          <t>It's getting close to midnight. When should I run the washing machine?</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1344,7 +1344,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>It's just past 5 PM, when should I run the washer?</t>
+          <t>It's just past 5 PM. When should I run the washer?</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1398,7 +1398,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>It's late afternoon, around 4 and I need to run the dryer. When should I start it?</t>
+          <t>It's late afternoon, around 4, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1452,7 +1452,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>It's late afternoon, around 4 and I'm trying to figure out when to start the washing machine. When should I run it?</t>
+          <t>It's late afternoon, around 4, and I'm trying to figure out when to start the washing machine. When should I run it?</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1668,7 +1668,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>It's late afternoon, around 4 and I need to run the dryer. When should I start it?</t>
+          <t>It's late afternoon, around 4, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1776,7 +1776,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>It's past 1 in the morning, when should I run the dryer?</t>
+          <t>It's past 1 in the morning. When should I run the dryer?</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1992,7 +1992,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>It's just past midnight, when should I run the dishwasher?</t>
+          <t>It's just past midnight. When should I run the dishwasher?</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>It's late afternoon, around 4 and I need to run the washing machine. When should I start it?</t>
+          <t>It's late afternoon, around 4, and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2154,7 +2154,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>It's mid-afternoon, about 2 and I'm trying to figure out when to start the dryer. When should I run it?</t>
+          <t>It's mid-afternoon, about 2, and I'm trying to figure out when to start the dryer. When should I run it?</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2262,7 +2262,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>It's around 8 at night, when should I run the dishwasher?</t>
+          <t>It's around 8 at night. When should I run the dishwasher?</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2586,7 +2586,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>It's mid-morning, about 10 and I need to run the dryer. When should I start it?</t>
+          <t>It's mid-morning, about 10, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2640,7 +2640,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>It's just past 9 AM, when should I run the dryer?</t>
+          <t>It's just past 9 AM. When should I run the dryer?</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2910,7 +2910,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>It's late morning, around 11 and I need to run the dishwasher. When should I start it?</t>
+          <t>It's late morning, around 11, and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3018,7 +3018,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>It's mid-morning, about 10 and I need to run the dishwasher. When should I start it?</t>
+          <t>It's mid-morning, about 10, and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3072,7 +3072,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>It's late afternoon, just past 3 and I need to run the washing machine. When should I start it?</t>
+          <t>It's late afternoon, just past 3, and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3126,7 +3126,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>It's just past 9 AM, when should I run the dryer?</t>
+          <t>It's just past 9 AM. When should I run the dryer?</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3288,7 +3288,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>It's late afternoon, around 4 and I need to run the washing machine. When should I start it?</t>
+          <t>It's late afternoon, around 4, and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3342,7 +3342,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>It's around 5 in the evening, when should I run the washing machine?</t>
+          <t>It's around 5 in the evening. When should I run the washing machine?</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3396,7 +3396,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>It's late afternoon, just past 3 and I need to run the dryer. When should I start it?</t>
+          <t>It's late afternoon, just past 3, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3450,7 +3450,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>It's just past 7 PM, when should I run the dryer?</t>
+          <t>It's just past 7 PM. When should I run the dryer?</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3612,7 +3612,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>It's late, just past 10 PM and I need to run the dryer. When should I start it?</t>
+          <t>It's late, just past 10 PM, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3774,7 +3774,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>It's getting close to midnight, when should I run the washing machine?</t>
+          <t>It's getting close to midnight. When should I run the washing machine?</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3882,7 +3882,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>It's mid-afternoon, about 2 and I need to run the dryer. When should I start it?</t>
+          <t>It's mid-afternoon, about 2, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3936,7 +3936,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>It's just after 8 AM, when should I run the dishwasher?</t>
+          <t>It's just after 9 AM. When should I run the dishwasher?</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4098,7 +4098,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>It's late morning, just before noon and I need to run the dryer. When should I start it?</t>
+          <t>It's late morning, just before noon, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4368,7 +4368,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>It's nearly 11 at night, when should I run the washing machine?</t>
+          <t>It's nearly 11 at night. When should I run the washing machine?</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4530,7 +4530,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>It's late afternoon, just past 3, when should I run the dishwasher?</t>
+          <t>It's late afternoon, just past 3. When should I run the dishwasher?</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5664,7 +5664,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>It's around 2 in the afternoon, when should I run the dryer?</t>
+          <t>It's around 2 in the afternoon. When should I run the dryer?</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -5804,22 +5804,22 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>6pm</t>
+          <t>6:00 PM</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>6pm</t>
+          <t>6:00 PM</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>10pm</t>
+          <t>10:00 PM</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>6am</t>
+          <t>6:00 AM</t>
         </is>
       </c>
     </row>
@@ -5858,22 +5858,22 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>8am</t>
+          <t>8:00 AM</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>8am</t>
+          <t>8:00 AM</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2pm</t>
+          <t>2:00 PM</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>11pm</t>
+          <t>11:00 PM</t>
         </is>
       </c>
     </row>
